--- a/Check.xlsx
+++ b/Check.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\AndroidStudioProjects\qamid-diplom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6572CCEB-A467-44D3-B6B6-411CAA52BC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEF1297-B8D2-4091-A238-1E54B4816852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5C029940-5AE2-4D89-8AD8-E3079AAAEA93}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5C029940-5AE2-4D89-8AD8-E3079AAAEA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="265">
   <si>
     <t>ID</t>
   </si>
@@ -799,6 +799,27 @@
   </si>
   <si>
     <t>Все кнопки, весь текст в приложении переведен на русский язык</t>
+  </si>
+  <si>
+    <t>Продено</t>
+  </si>
+  <si>
+    <t>Провал</t>
+  </si>
+  <si>
+    <t>Кнопка About некликабельна</t>
+  </si>
+  <si>
+    <t>Чекбокс некликабелен. Необходимо уточнить требования</t>
+  </si>
+  <si>
+    <t>Дата не соответствует</t>
+  </si>
+  <si>
+    <t>Возможно выбрать время ранее текущего. Необходимо уточнить требования</t>
+  </si>
+  <si>
+    <t>Поле не ограничено по длине</t>
   </si>
 </sst>
 </file>
@@ -1192,6 +1213,9 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
+      <c r="E2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1206,6 +1230,9 @@
       <c r="D3" t="s">
         <v>9</v>
       </c>
+      <c r="E3" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1220,6 +1247,9 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
+      <c r="E4" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1234,6 +1264,9 @@
       <c r="D5" t="s">
         <v>9</v>
       </c>
+      <c r="E5" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1248,6 +1281,9 @@
       <c r="D6" t="s">
         <v>18</v>
       </c>
+      <c r="E6" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1262,6 +1298,9 @@
       <c r="D7" t="s">
         <v>18</v>
       </c>
+      <c r="E7" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1276,6 +1315,9 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
+      <c r="E8" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1290,6 +1332,9 @@
       <c r="D9" t="s">
         <v>9</v>
       </c>
+      <c r="E9" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1304,6 +1349,9 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1318,6 +1366,9 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1332,6 +1383,9 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1346,6 +1400,9 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1360,6 +1417,9 @@
       <c r="D14" t="s">
         <v>9</v>
       </c>
+      <c r="E14" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1374,6 +1434,9 @@
       <c r="D15" t="s">
         <v>9</v>
       </c>
+      <c r="E15" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1388,8 +1451,11 @@
       <c r="D16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1402,8 +1468,11 @@
       <c r="D17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1416,8 +1485,14 @@
       <c r="D18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" t="s">
+        <v>259</v>
+      </c>
+      <c r="F18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -1430,8 +1505,11 @@
       <c r="D19" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -1444,8 +1522,11 @@
       <c r="D20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1458,8 +1539,11 @@
       <c r="D21" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1472,8 +1556,11 @@
       <c r="D22" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1486,8 +1573,11 @@
       <c r="D23" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1500,8 +1590,11 @@
       <c r="D24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1514,8 +1607,11 @@
       <c r="D25" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -1528,8 +1624,11 @@
       <c r="D26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -1542,8 +1641,11 @@
       <c r="D27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -1556,8 +1658,11 @@
       <c r="D28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -1570,8 +1675,11 @@
       <c r="D29" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -1584,8 +1692,11 @@
       <c r="D30" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -1598,8 +1709,11 @@
       <c r="D31" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>72</v>
       </c>
@@ -1612,8 +1726,11 @@
       <c r="D32" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1626,8 +1743,11 @@
       <c r="D33" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>77</v>
       </c>
@@ -1640,8 +1760,11 @@
       <c r="D34" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1654,8 +1777,11 @@
       <c r="D35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1668,8 +1794,11 @@
       <c r="D36" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1682,8 +1811,11 @@
       <c r="D37" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1696,8 +1828,11 @@
       <c r="D38" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1710,8 +1845,11 @@
       <c r="D39" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1724,8 +1862,11 @@
       <c r="D40" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1738,8 +1879,11 @@
       <c r="D41" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -1752,8 +1896,11 @@
       <c r="D42" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -1766,8 +1913,11 @@
       <c r="D43" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>97</v>
       </c>
@@ -1780,8 +1930,11 @@
       <c r="D44" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -1794,8 +1947,11 @@
       <c r="D45" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -1808,8 +1964,11 @@
       <c r="D46" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -1822,8 +1981,11 @@
       <c r="D47" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>105</v>
       </c>
@@ -1836,8 +1998,11 @@
       <c r="D48" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>107</v>
       </c>
@@ -1850,8 +2015,11 @@
       <c r="D49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E49" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>109</v>
       </c>
@@ -1864,8 +2032,11 @@
       <c r="D50" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E50" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>111</v>
       </c>
@@ -1878,8 +2049,11 @@
       <c r="D51" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E51" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>113</v>
       </c>
@@ -1892,8 +2066,11 @@
       <c r="D52" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>115</v>
       </c>
@@ -1906,8 +2083,11 @@
       <c r="D53" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E53" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -1920,8 +2100,11 @@
       <c r="D54" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>119</v>
       </c>
@@ -1934,8 +2117,11 @@
       <c r="D55" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E55" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>122</v>
       </c>
@@ -1948,8 +2134,11 @@
       <c r="D56" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E56" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>124</v>
       </c>
@@ -1962,8 +2151,11 @@
       <c r="D57" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E57" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>126</v>
       </c>
@@ -1976,8 +2168,11 @@
       <c r="D58" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E58" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -1990,8 +2185,11 @@
       <c r="D59" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E59" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>130</v>
       </c>
@@ -2004,8 +2202,11 @@
       <c r="D60" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E60" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>132</v>
       </c>
@@ -2018,8 +2219,11 @@
       <c r="D61" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E61" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>134</v>
       </c>
@@ -2032,8 +2236,11 @@
       <c r="D62" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E62" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>136</v>
       </c>
@@ -2046,8 +2253,11 @@
       <c r="D63" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E63" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>138</v>
       </c>
@@ -2060,8 +2270,11 @@
       <c r="D64" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E64" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>140</v>
       </c>
@@ -2074,8 +2287,11 @@
       <c r="D65" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E65" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>143</v>
       </c>
@@ -2088,8 +2304,11 @@
       <c r="D66" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E66" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>145</v>
       </c>
@@ -2102,8 +2321,11 @@
       <c r="D67" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E67" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>147</v>
       </c>
@@ -2116,8 +2338,11 @@
       <c r="D68" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E68" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>149</v>
       </c>
@@ -2130,8 +2355,11 @@
       <c r="D69" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E69" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>151</v>
       </c>
@@ -2144,8 +2372,11 @@
       <c r="D70" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E70" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>153</v>
       </c>
@@ -2158,8 +2389,14 @@
       <c r="D71" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E71" t="s">
+        <v>259</v>
+      </c>
+      <c r="F71" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>155</v>
       </c>
@@ -2172,8 +2409,11 @@
       <c r="D72" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E72" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>157</v>
       </c>
@@ -2186,8 +2426,11 @@
       <c r="D73" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E73" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>159</v>
       </c>
@@ -2200,8 +2443,11 @@
       <c r="D74" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E74" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>161</v>
       </c>
@@ -2214,8 +2460,11 @@
       <c r="D75" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E75" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>163</v>
       </c>
@@ -2228,8 +2477,11 @@
       <c r="D76" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E76" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>165</v>
       </c>
@@ -2242,8 +2494,14 @@
       <c r="D77" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E77" t="s">
+        <v>259</v>
+      </c>
+      <c r="F77" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>167</v>
       </c>
@@ -2256,8 +2514,11 @@
       <c r="D78" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E78" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>169</v>
       </c>
@@ -2270,8 +2531,11 @@
       <c r="D79" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E79" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>171</v>
       </c>
@@ -2284,8 +2548,11 @@
       <c r="D80" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E80" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>173</v>
       </c>
@@ -2298,8 +2565,11 @@
       <c r="D81" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E81" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>175</v>
       </c>
@@ -2312,8 +2582,11 @@
       <c r="D82" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E82" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>177</v>
       </c>
@@ -2326,8 +2599,14 @@
       <c r="D83" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E83" t="s">
+        <v>259</v>
+      </c>
+      <c r="F83" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>179</v>
       </c>
@@ -2340,8 +2619,14 @@
       <c r="D84" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E84" t="s">
+        <v>259</v>
+      </c>
+      <c r="F84" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>181</v>
       </c>
@@ -2354,8 +2639,11 @@
       <c r="D85" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>183</v>
       </c>
@@ -2368,8 +2656,14 @@
       <c r="D86" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E86" t="s">
+        <v>259</v>
+      </c>
+      <c r="F86" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>185</v>
       </c>
@@ -2382,8 +2676,11 @@
       <c r="D87" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E87" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>188</v>
       </c>
@@ -2396,8 +2693,11 @@
       <c r="D88" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E88" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>190</v>
       </c>
@@ -2410,8 +2710,11 @@
       <c r="D89" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E89" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>193</v>
       </c>
@@ -2424,8 +2727,11 @@
       <c r="D90" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E90" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>195</v>
       </c>
@@ -2438,8 +2744,11 @@
       <c r="D91" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E91" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>197</v>
       </c>
@@ -2452,8 +2761,11 @@
       <c r="D92" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E92" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>199</v>
       </c>
@@ -2466,8 +2778,11 @@
       <c r="D93" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E93" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -2480,8 +2795,11 @@
       <c r="D94" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E94" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>203</v>
       </c>
@@ -2494,8 +2812,11 @@
       <c r="D95" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E95" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>205</v>
       </c>
@@ -2508,8 +2829,11 @@
       <c r="D96" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E96" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>207</v>
       </c>
@@ -2522,8 +2846,11 @@
       <c r="D97" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E97" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>209</v>
       </c>
@@ -2536,8 +2863,11 @@
       <c r="D98" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E98" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>211</v>
       </c>
@@ -2550,8 +2880,11 @@
       <c r="D99" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E99" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>213</v>
       </c>
@@ -2564,8 +2897,11 @@
       <c r="D100" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E100" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>215</v>
       </c>
@@ -2578,8 +2914,11 @@
       <c r="D101" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E101" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>217</v>
       </c>
@@ -2592,8 +2931,14 @@
       <c r="D102" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E102" t="s">
+        <v>259</v>
+      </c>
+      <c r="F102" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>219</v>
       </c>
@@ -2606,8 +2951,11 @@
       <c r="D103" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E103" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>221</v>
       </c>
@@ -2620,8 +2968,11 @@
       <c r="D104" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E104" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>223</v>
       </c>
@@ -2634,8 +2985,11 @@
       <c r="D105" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E105" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -2648,8 +3002,11 @@
       <c r="D106" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E106" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>227</v>
       </c>
@@ -2662,8 +3019,14 @@
       <c r="D107" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E107" t="s">
+        <v>259</v>
+      </c>
+      <c r="F107" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>229</v>
       </c>
@@ -2676,8 +3039,11 @@
       <c r="D108" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E108" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>233</v>
       </c>
@@ -2690,8 +3056,11 @@
       <c r="D109" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E109" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>235</v>
       </c>
@@ -2704,8 +3073,11 @@
       <c r="D110" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E110" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>237</v>
       </c>
@@ -2718,8 +3090,11 @@
       <c r="D111" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E111" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>237</v>
       </c>
@@ -2732,8 +3107,11 @@
       <c r="D112" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E112" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>240</v>
       </c>
@@ -2746,8 +3124,11 @@
       <c r="D113" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E113" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>243</v>
       </c>
@@ -2760,8 +3141,11 @@
       <c r="D114" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E114" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>245</v>
       </c>
@@ -2774,8 +3158,11 @@
       <c r="D115" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E115" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>247</v>
       </c>
@@ -2788,8 +3175,11 @@
       <c r="D116" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E116" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>249</v>
       </c>
@@ -2802,8 +3192,11 @@
       <c r="D117" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E117" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>251</v>
       </c>
@@ -2816,8 +3209,11 @@
       <c r="D118" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E118" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>253</v>
       </c>
@@ -2830,8 +3226,11 @@
       <c r="D119" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E119" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>255</v>
       </c>
@@ -2843,6 +3242,9 @@
       </c>
       <c r="D120" t="s">
         <v>9</v>
+      </c>
+      <c r="E120" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
